--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -878,45 +878,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130382898</v>
+        <v>130382893</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604698</v>
+        <v>604724</v>
       </c>
       <c r="R4" t="n">
-        <v>6675460</v>
+        <v>6675482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,11 +953,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,49 +980,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130382893</v>
+        <v>130382898</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604724</v>
+        <v>604698</v>
       </c>
       <c r="R5" t="n">
-        <v>6675482</v>
+        <v>6675460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,6 +1051,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130382897</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130382891</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>130382893</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>130382898</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>130382903</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>130382892</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130382896</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>130382894</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130382890</v>
       </c>
       <c r="B10" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130382897</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130382891</v>
       </c>
       <c r="B3" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,49 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130382893</v>
+        <v>130382898</v>
       </c>
       <c r="B4" t="n">
-        <v>98923</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604724</v>
+        <v>604698</v>
       </c>
       <c r="R4" t="n">
-        <v>6675482</v>
+        <v>6675460</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +949,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,45 +981,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130382898</v>
+        <v>130382893</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>98949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604698</v>
+        <v>604724</v>
       </c>
       <c r="R5" t="n">
-        <v>6675460</v>
+        <v>6675482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,11 +1056,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,7 +1086,7 @@
         <v>130382903</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>130382892</v>
       </c>
       <c r="B7" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130382896</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>130382894</v>
       </c>
       <c r="B9" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130382890</v>
       </c>
       <c r="B10" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>130422422</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130382891</v>
       </c>
       <c r="B3" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,45 +878,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130382898</v>
+        <v>130382893</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>98950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604698</v>
+        <v>604724</v>
       </c>
       <c r="R4" t="n">
-        <v>6675460</v>
+        <v>6675482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,11 +953,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,49 +980,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130382893</v>
+        <v>130382898</v>
       </c>
       <c r="B5" t="n">
-        <v>98949</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604724</v>
+        <v>604698</v>
       </c>
       <c r="R5" t="n">
-        <v>6675482</v>
+        <v>6675460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,6 +1051,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,7 +1183,7 @@
         <v>130382892</v>
       </c>
       <c r="B7" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130382890</v>
       </c>
       <c r="B10" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130382891</v>
       </c>
       <c r="B3" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,49 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130382893</v>
+        <v>130382898</v>
       </c>
       <c r="B4" t="n">
-        <v>98950</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604724</v>
+        <v>604698</v>
       </c>
       <c r="R4" t="n">
-        <v>6675482</v>
+        <v>6675460</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +949,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,45 +981,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130382898</v>
+        <v>130382893</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>98951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604698</v>
+        <v>604724</v>
       </c>
       <c r="R5" t="n">
-        <v>6675460</v>
+        <v>6675482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,11 +1056,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,7 +1183,7 @@
         <v>130382892</v>
       </c>
       <c r="B7" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130382890</v>
       </c>
       <c r="B10" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130382897</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130382891</v>
       </c>
       <c r="B3" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>130382898</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>130382893</v>
       </c>
       <c r="B5" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>130382903</v>
       </c>
       <c r="B6" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>130382892</v>
       </c>
       <c r="B7" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130382896</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>130382894</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130382890</v>
       </c>
       <c r="B10" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>130422422</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130382891</v>
       </c>
       <c r="B3" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,45 +878,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130382898</v>
+        <v>130382893</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>98957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604698</v>
+        <v>604724</v>
       </c>
       <c r="R4" t="n">
-        <v>6675460</v>
+        <v>6675482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,11 +953,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,49 +980,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130382893</v>
+        <v>130382898</v>
       </c>
       <c r="B5" t="n">
-        <v>98953</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604724</v>
+        <v>604698</v>
       </c>
       <c r="R5" t="n">
-        <v>6675482</v>
+        <v>6675460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,6 +1051,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,7 +1183,7 @@
         <v>130382892</v>
       </c>
       <c r="B7" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130382890</v>
       </c>
       <c r="B10" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -878,49 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130382893</v>
+        <v>130382898</v>
       </c>
       <c r="B4" t="n">
-        <v>98957</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604724</v>
+        <v>604698</v>
       </c>
       <c r="R4" t="n">
-        <v>6675482</v>
+        <v>6675460</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +949,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,45 +981,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130382898</v>
+        <v>130382893</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>98957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604698</v>
+        <v>604724</v>
       </c>
       <c r="R5" t="n">
-        <v>6675460</v>
+        <v>6675482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,11 +1056,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130382897</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130382891</v>
       </c>
       <c r="B3" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,45 +878,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130382898</v>
+        <v>130382893</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>98970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604698</v>
+        <v>604724</v>
       </c>
       <c r="R4" t="n">
-        <v>6675460</v>
+        <v>6675482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,11 +953,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,49 +980,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130382893</v>
+        <v>130382898</v>
       </c>
       <c r="B5" t="n">
-        <v>98957</v>
+        <v>79219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604724</v>
+        <v>604698</v>
       </c>
       <c r="R5" t="n">
-        <v>6675482</v>
+        <v>6675460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,6 +1051,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,7 +1086,7 @@
         <v>130382903</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>130382892</v>
       </c>
       <c r="B7" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130382896</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>130382894</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130382890</v>
       </c>
       <c r="B10" t="n">
-        <v>97828</v>
+        <v>97841</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>130422422</v>
       </c>
       <c r="B11" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130382897</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130382891</v>
       </c>
       <c r="B3" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,49 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130382893</v>
+        <v>130382898</v>
       </c>
       <c r="B4" t="n">
-        <v>98970</v>
+        <v>79220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604724</v>
+        <v>604698</v>
       </c>
       <c r="R4" t="n">
-        <v>6675482</v>
+        <v>6675460</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +949,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,45 +981,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130382898</v>
+        <v>130382893</v>
       </c>
       <c r="B5" t="n">
-        <v>79219</v>
+        <v>98971</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604698</v>
+        <v>604724</v>
       </c>
       <c r="R5" t="n">
-        <v>6675460</v>
+        <v>6675482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,11 +1056,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,7 +1086,7 @@
         <v>130382903</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>130382892</v>
       </c>
       <c r="B7" t="n">
-        <v>98970</v>
+        <v>98971</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130382896</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>130382894</v>
       </c>
       <c r="B9" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130382890</v>
       </c>
       <c r="B10" t="n">
-        <v>97841</v>
+        <v>97842</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>130422422</v>
       </c>
       <c r="B11" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130382897</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130382891</v>
       </c>
       <c r="B3" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,45 +878,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130382898</v>
+        <v>130382893</v>
       </c>
       <c r="B4" t="n">
-        <v>79220</v>
+        <v>98974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604698</v>
+        <v>604724</v>
       </c>
       <c r="R4" t="n">
-        <v>6675460</v>
+        <v>6675482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,11 +953,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,49 +980,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130382893</v>
+        <v>130382898</v>
       </c>
       <c r="B5" t="n">
-        <v>98971</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604724</v>
+        <v>604698</v>
       </c>
       <c r="R5" t="n">
-        <v>6675482</v>
+        <v>6675460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,6 +1051,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,7 +1086,7 @@
         <v>130382903</v>
       </c>
       <c r="B6" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>130382892</v>
       </c>
       <c r="B7" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130382896</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>130382894</v>
       </c>
       <c r="B9" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130382890</v>
       </c>
       <c r="B10" t="n">
-        <v>97842</v>
+        <v>97845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>130422422</v>
       </c>
       <c r="B11" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -878,49 +878,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130382893</v>
+        <v>130382898</v>
       </c>
       <c r="B4" t="n">
-        <v>98974</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604724</v>
+        <v>604698</v>
       </c>
       <c r="R4" t="n">
-        <v>6675482</v>
+        <v>6675460</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -953,6 +949,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,45 +981,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130382898</v>
+        <v>130382893</v>
       </c>
       <c r="B5" t="n">
-        <v>79221</v>
+        <v>98974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604698</v>
+        <v>604724</v>
       </c>
       <c r="R5" t="n">
-        <v>6675460</v>
+        <v>6675482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,11 +1056,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130382891</v>
       </c>
       <c r="B3" t="n">
-        <v>98974</v>
+        <v>98988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>130382893</v>
       </c>
       <c r="B5" t="n">
-        <v>98974</v>
+        <v>98988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>130382892</v>
       </c>
       <c r="B7" t="n">
-        <v>98974</v>
+        <v>98988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130382890</v>
       </c>
       <c r="B10" t="n">
-        <v>97845</v>
+        <v>97854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>130382891</v>
       </c>
       <c r="B3" t="n">
-        <v>98988</v>
+        <v>98989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>130382893</v>
       </c>
       <c r="B5" t="n">
-        <v>98988</v>
+        <v>98989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>130382892</v>
       </c>
       <c r="B7" t="n">
-        <v>98988</v>
+        <v>98989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -1576,7 +1576,7 @@
         <v>130422422</v>
       </c>
       <c r="B11" t="n">
-        <v>57861</v>
+        <v>57875</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130382897</v>
+        <v>130382894</v>
       </c>
       <c r="B2" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604704</v>
+        <v>604698</v>
       </c>
       <c r="R2" t="n">
-        <v>6675460</v>
+        <v>6675454</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130382891</v>
+        <v>130382896</v>
       </c>
       <c r="B3" t="n">
-        <v>98989</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,43 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604703</v>
+        <v>604714</v>
       </c>
       <c r="R3" t="n">
-        <v>6675482</v>
+        <v>6675464</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,14 +874,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130382898</v>
+        <v>130382897</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -913,7 +909,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604698</v>
+        <v>604704</v>
       </c>
       <c r="R4" t="n">
         <v>6675460</v>
@@ -951,18 +947,12 @@
           <t>2025-12-18</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130382893</v>
+        <v>130382898</v>
       </c>
       <c r="B5" t="n">
-        <v>98989</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,38 +982,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604724</v>
+        <v>604698</v>
       </c>
       <c r="R5" t="n">
-        <v>6675482</v>
+        <v>6675460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,11 +1077,11 @@
         <v>130382903</v>
       </c>
       <c r="B6" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1180,32 +1171,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130382892</v>
+        <v>130422422</v>
       </c>
       <c r="B7" t="n">
-        <v>98989</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604701</v>
+        <v>604614</v>
       </c>
       <c r="R7" t="n">
-        <v>6675478</v>
+        <v>6675449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1236,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hackspår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1261,6 +1257,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1277,45 +1288,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130382896</v>
+        <v>130451761</v>
       </c>
       <c r="B8" t="n">
-        <v>79221</v>
+        <v>4775</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nordansjö naturreservat, Upl</t>
+          <t>Nordasjo Naturresevat, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604714</v>
+        <v>604591</v>
       </c>
       <c r="R8" t="n">
-        <v>6675464</v>
+        <v>6675395</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,12 +1358,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1356,6 +1372,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1374,45 +1391,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130382894</v>
+        <v>130405706</v>
       </c>
       <c r="B9" t="n">
-        <v>79221</v>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604698</v>
+        <v>604590</v>
       </c>
       <c r="R9" t="n">
-        <v>6675454</v>
+        <v>6675395</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,17 +1461,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1458,6 +1475,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1476,10 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130382890</v>
+        <v>130405705</v>
       </c>
       <c r="B10" t="n">
-        <v>97854</v>
+        <v>5199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1505,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604601</v>
+        <v>604590</v>
       </c>
       <c r="R10" t="n">
-        <v>6675416</v>
+        <v>6675396</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1541,12 +1559,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,45 +1591,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130422422</v>
+        <v>130382891</v>
       </c>
       <c r="B11" t="n">
-        <v>57875</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604614</v>
+        <v>604703</v>
       </c>
       <c r="R11" t="n">
-        <v>6675449</v>
+        <v>6675482</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1638,17 +1665,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>hackspår</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1659,21 +1681,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1690,32 +1697,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130405705</v>
+        <v>130382892</v>
       </c>
       <c r="B12" t="n">
-        <v>5197</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1725,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604590</v>
+        <v>604701</v>
       </c>
       <c r="R12" t="n">
-        <v>6675396</v>
+        <v>6675478</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,12 +1762,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,50 +1794,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130451761</v>
+        <v>130382893</v>
       </c>
       <c r="B13" t="n">
-        <v>4773</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nordasjo Naturresevat, Upl</t>
+          <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604591</v>
+        <v>604724</v>
       </c>
       <c r="R13" t="n">
-        <v>6675395</v>
+        <v>6675482</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,12 +1863,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1890,10 +1896,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130405706</v>
+        <v>130382890</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>97983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1901,39 +1907,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nordansjö naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604590</v>
+        <v>604601</v>
       </c>
       <c r="R14" t="n">
-        <v>6675395</v>
+        <v>6675416</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1960,12 +1961,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1974,7 +1975,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1990,6 +1990,103 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130382889</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nordansjö naturreservat, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>604704</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6675454</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54339-2025 artfynd.xlsx
+++ b/artfynd/A 54339-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130382894</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130382896</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130382897</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,6 +1091,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130382898</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1168,6 +1193,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130382903</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1285,6 +1315,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130422422</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130451761</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130405706</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1588,6 +1633,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130405705</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1694,6 +1744,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130382891</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1791,6 +1846,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130382892</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130382893</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130382890</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2087,8 +2157,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130382889</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>